--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jul-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/jul-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M113"/>
+  <dimension ref="A1:M107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -565,11 +565,11 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>3289174.28</v>
+        <v>3533.06</v>
       </c>
     </row>
     <row r="3">
@@ -626,17 +626,17 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>8638946.609999999</v>
+        <v>9279.51</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1380-8310-CM26</t>
+          <t>1057539-5011-CM26</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,53 +651,53 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Enviada a Proveedor</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>13875565.41</v>
+        <v>4449.84</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2111-10243-CM26</t>
+          <t>2069-5912-CM26</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -717,17 +717,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Enviada a Proveedor</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,28 +737,28 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TECNOMEDICAL S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>99.585.860-6</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>10115000</v>
+        <v>3477.5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1057539-5011-CM26</t>
+          <t>2069-5911-CM26</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -778,22 +778,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -809,17 +809,17 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>4142667.27</v>
+        <v>5250.21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2069-5934-CM26</t>
+          <t>2069-5908-CM26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -870,17 +870,17 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3417207.57</v>
+        <v>12723.89</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2069-5912-CM26</t>
+          <t>2069-5528-CM26</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -931,17 +931,17 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3237444.98</v>
+        <v>5437.12</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2069-5911-CM26</t>
+          <t>2069-5934-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -992,17 +992,17 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>4887790.53</v>
+        <v>3670.59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2069-5908-CM26</t>
+          <t>2069-5525-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1053,17 +1053,17 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>11845559.88</v>
+        <v>3500.14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2069-5526-CM26</t>
+          <t>2069-5522-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1114,17 +1114,17 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2175711.51</v>
+        <v>3770.04</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2069-5528-CM26</t>
+          <t>2069-5517-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,17 +1175,17 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>5061794.71</v>
+        <v>3477.5</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2069-5522-CM26</t>
+          <t>1691-1231-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1210,43 +1210,43 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>3509795.52</v>
+        <v>4908.43</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2069-5517-CM26</t>
+          <t>1057431-1636-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.602.295-4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO NAC DE SALUD HOSPITAL TRAUMATOLOGICO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1297,17 +1297,17 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3237444.98</v>
+        <v>67074.3</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2111-9684-CM26</t>
+          <t>2069-5526-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1327,17 +1327,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Enviada a Proveedor</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,28 +1347,28 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>TECNOMEDICAL S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>99.585.860-6</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>10115000</v>
+        <v>2337.04</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>1691-1231-CM26</t>
+          <t>3378-5622-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1393,43 +1393,43 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>4569600</v>
+        <v>4061.36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2111-9619-CM26</t>
+          <t>5326-867-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,53 +1444,53 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Enviada a Proveedor</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>TECNOMEDICAL S A</t>
+          <t>GLOBALMED SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>99.585.860-6</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3034500</v>
+        <v>47835.83</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1057431-1636-CM26</t>
+          <t>2069-6030-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1505,27 +1505,27 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.602.295-4</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERVICIO NAC DE SALUD HOSPITAL TRAUMATOLOGICO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1541,17 +1541,17 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>62444162.34</v>
+        <v>7341.18</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2069-5525-CM26</t>
+          <t>2069-5521-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1602,17 +1602,17 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>3258527.02</v>
+        <v>8011.34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3378-5622-CM26</t>
+          <t>2069-6029-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,7 +1627,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1637,12 +1637,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1663,17 +1663,17 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3781008.42</v>
+        <v>3298.79</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>5326-867-CM26</t>
+          <t>812030-704-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,7 +1688,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,43 +1698,43 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>44533727</v>
+        <v>10411.24</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2069-6030-CM26</t>
+          <t>5326-868-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,53 +1749,53 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>6834415.14</v>
+        <v>16923.85</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2069-5521-CM26</t>
+          <t>5326-869-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,53 +1810,53 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>7458315.48</v>
+        <v>38308.75</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2069-6029-CM26</t>
+          <t>1057539-5169-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1871,27 +1871,27 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1907,17 +1907,17 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>3071071.08</v>
+        <v>7681.31</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1057539-5169-CM26</t>
+          <t>1057489-8316-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1932,53 +1932,53 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.406-2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>7151067</v>
+        <v>24313.46</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5326-869-CM26</t>
+          <t>3391-455-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,53 +1993,53 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>76.901.400-4</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>35664300</v>
+        <v>2442.08</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>812030-704-CM26</t>
+          <t>1057539-5087-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,43 +2064,43 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>9692550</v>
+        <v>3506.14</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5326-868-CM26</t>
+          <t>4967-1297-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2115,47 +2115,47 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.606.604-8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>HOSPITAL DE QUILPUE</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>96.533.330-4</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>15755600</v>
+        <v>2492.56</v>
       </c>
     </row>
     <row r="29">
@@ -2212,17 +2212,17 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>6247500</v>
+        <v>6710.74</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>4967-1297-CM26</t>
+          <t>2069-5913-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2247,43 +2247,43 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.606.604-8</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>HOSPITAL DE QUILPUE</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2320500</v>
+        <v>8724.41</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2069-5913-CM26</t>
+          <t>1057439-4572-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2298,53 +2298,53 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>8122165.31</v>
+        <v>8234.34</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1057539-5087-CM26</t>
+          <t>1057402-7006-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2359,53 +2359,53 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3264108.12</v>
+        <v>7289.48</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>3391-455-CM26</t>
+          <t>1057402-7196-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2420,7 +2420,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2430,43 +2430,43 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>2273498.57</v>
+        <v>6446.79</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>1057489-8316-CM26</t>
+          <t>1057402-7241-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -2491,17 +2491,17 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.608.406-2</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2517,17 +2517,17 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>22635101.86</v>
+        <v>3733.82</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>1057402-7247-CM26</t>
+          <t>1057402-7245-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2578,17 +2578,17 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>5461325.31</v>
+        <v>4295</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1063538-5042-CM26</t>
+          <t>1057402-7247-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2613,43 +2613,43 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.602.260-1</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>HOSPITAL BASE OSORNO</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Spinex Corporation Chile S.A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>76.166.489-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>7220986.64</v>
+        <v>5866.27</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>1057439-4572-CM26</t>
+          <t>1057402-7271-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2669,42 +2669,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>7665926.45</v>
+        <v>3733.82</v>
       </c>
     </row>
     <row r="38">
@@ -2761,17 +2761,17 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>5325495.14</v>
+        <v>5720.37</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>1057402-7271-CM26</t>
+          <t>1063538-5042-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2796,43 +2796,43 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.602.260-1</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL BASE OSORNO</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>Spinex Corporation Chile S.A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.166.489-1</t>
         </is>
       </c>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>3476072.11</v>
+        <v>7756.41</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1057402-7245-CM26</t>
+          <t>3191-3409-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2847,53 +2847,53 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>3998517.81</v>
+        <v>6398.63</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1057402-7241-CM26</t>
+          <t>1057491-4113-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2918,43 +2918,43 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>NEUMANN LIMITADA</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>78.936.310-2</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>3476072.11</v>
+        <v>11949.35</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1057402-7196-CM26</t>
+          <t>3391-464-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -2969,53 +2969,53 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>6001765</v>
+        <v>2832.43</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1057402-7006-CM26</t>
+          <t>1057417-13650-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3040,43 +3040,43 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>6786284.4</v>
+        <v>5330.25</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1057417-13650-CM26</t>
+          <t>1549-3011-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3091,53 +3091,53 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>4962300</v>
+        <v>67215.66</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>3391-464-CM26</t>
+          <t>2069-6356-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3152,27 +3152,27 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3188,17 +3188,17 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>2636904.34</v>
+        <v>13195.15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1057491-4113-CM26</t>
+          <t>1057539-5481-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3213,53 +3213,53 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>NEUMANN LIMITADA</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>78.936.310-2</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>11124481.76</v>
+        <v>3205.05</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>3191-3409-CM26</t>
+          <t>3391-467-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3284,43 +3284,43 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>61.101.086-9</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>Ejercito de Chile</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>5956934.13</v>
+        <v>4061.36</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1549-3011-CM26</t>
+          <t>2069-6352-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3335,22 +3335,22 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -3360,28 +3360,28 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>62575763.25</v>
+        <v>4075.79</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>3391-467-CM26</t>
+          <t>3378-6046-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3401,22 +3401,22 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.101.086-9</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ejercito de Chile</t>
+          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3432,17 +3432,17 @@
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>3781008.42</v>
+        <v>4061.36</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2069-6356-CM26</t>
+          <t>2069-6191-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3493,17 +3493,17 @@
       <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>12284284.32</v>
+        <v>7543.72</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>1057539-5481-CM26</t>
+          <t>2069-6189-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3523,48 +3523,48 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>2983806</v>
+        <v>10838.87</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2069-6352-CM26</t>
+          <t>1691-1273-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3589,43 +3589,43 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
       <c r="L52" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>3794434</v>
+        <v>4024.91</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>3378-6046-CM26</t>
+          <t>1057503-3428-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3645,17 +3645,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.958.500-3</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>Hospital Padre Alberto Hurtado</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -3665,28 +3665,28 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>3781008.42</v>
+        <v>42820.93</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2069-6191-CM26</t>
+          <t>5349-1405-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3711,43 +3711,43 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.606.303-0</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>7022974.21</v>
+        <v>2347.87</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2069-6189-CM26</t>
+          <t>1057503-3492-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3762,22 +3762,22 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.958.500-3</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>Hospital Padre Alberto Hurtado</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3787,28 +3787,28 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>10090662.12</v>
+        <v>14717.83</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1691-1273-CM26</t>
+          <t>1057501-7822-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3823,53 +3823,53 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>92.288.000-k</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>3747072</v>
+        <v>4090.36</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1057503-3428-CM26</t>
+          <t>1057882-9-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3884,22 +3884,22 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.958.500-3</t>
+          <t>61.959.800-8</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3909,28 +3909,28 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>HEMISFERIO SUR S.A.</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>96.533.330-4</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>39865000</v>
+        <v>17447.93</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1057503-3492-CM26</t>
+          <t>3378-6087-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3945,7 +3945,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>61.958.500-3</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hospital Padre Alberto Hurtado</t>
+          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3981,17 +3981,17 @@
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>13701862.3</v>
+        <v>2683.93</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1057501-7822-CM26</t>
+          <t>812030-753-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4016,12 +4016,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -4031,28 +4031,28 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3808000</v>
+        <v>4177.28</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>5349-1405-CM26</t>
+          <t>1075337-8967-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4067,53 +4067,53 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.602.222-9</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>GLOBALMED SPA</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>2185792</v>
+        <v>6265.2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1057882-9-CM26</t>
+          <t>1057491-4167-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4138,12 +4138,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.959.800-8</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>HOSPITAL ORIENTE DR LUIS TISNE BROUSSE</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4153,28 +4153,28 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>NEUMANN LIMITADA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
+          <t>78.936.310-2</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
       <c r="L61" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>16243500</v>
+        <v>11949.35</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>3378-6087-CM26</t>
+          <t>1063538-5132-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4199,43 +4199,43 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.602.260-1</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>HOSPITAL BASE OSORNO</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>Spinex Corporation Chile S.A</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.166.489-1</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2498660.85</v>
+        <v>9279.51</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>812030-753-CM26</t>
+          <t>1057501-7879-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4260,12 +4260,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -4286,17 +4286,17 @@
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3888920</v>
+        <v>73626.42999999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1075337-8967-CM26</t>
+          <t>1057402-7509-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4311,53 +4311,53 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.602.222-9</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA NORTE HOSPITAL DE ANGOL</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K64" t="inlineStr"/>
       <c r="L64" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>5832713.6</v>
+        <v>4211.23</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>1057491-4167-CM26</t>
+          <t>1057402-7511-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4372,7 +4372,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -4382,43 +4382,43 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>NEUMANN LIMITADA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>78.936.310-2</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>11124481.76</v>
+        <v>4295</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>1063538-5132-CM26</t>
+          <t>1057402-7447-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4433,53 +4433,53 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.602.260-1</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>HOSPITAL BASE OSORNO</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Spinex Corporation Chile S.A</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.166.489-1</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>8638946.609999999</v>
+        <v>6343.69</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>1057501-7879-CM26</t>
+          <t>1691-1379-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4504,43 +4504,43 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.602.280-6</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>68544000</v>
+        <v>13498.18</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>1057402-7511-CM26</t>
+          <t>1057402-7507-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4591,17 +4591,17 @@
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3998517.81</v>
+        <v>3733.82</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>1057402-7509-CM26</t>
+          <t>608-7752-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4616,53 +4616,53 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3920531.16</v>
+        <v>47450.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>1691-1379-CM26</t>
+          <t>3328-1722-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4677,53 +4677,53 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.602.280-6</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE C</t>
+          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>12566400</v>
+        <v>4415.74</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1057402-7447-CM26</t>
+          <t>3328-1751-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4748,43 +4748,43 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>5905784.36</v>
+        <v>5460.62</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1057402-7507-CM26</t>
+          <t>1057539-5660-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4799,53 +4799,53 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3476072.11</v>
+        <v>11687.12</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>608-7752-CM26</t>
+          <t>1430708-120-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4870,43 +4870,43 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.606.403-7</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>44175180</v>
+        <v>4315.43</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>3328-1722-CM26</t>
+          <t>812030-765-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4921,22 +4921,22 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -4946,28 +4946,28 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>4110919.26</v>
+        <v>10411.24</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>3328-1751-CM26</t>
+          <t>1057501-7867-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4992,12 +4992,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -5018,17 +5018,17 @@
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>5083670.48</v>
+        <v>57719.28</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>1057539-5660-CM26</t>
+          <t>1057501-7870-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5043,27 +5043,27 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5079,17 +5079,17 @@
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>10880360.4</v>
+        <v>55328.92</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1430708-120-CM26</t>
+          <t>1057501-7871-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5104,7 +5104,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5114,17 +5114,17 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.606.403-7</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE COQUIMBO</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5140,17 +5140,17 @@
       <c r="K77" t="inlineStr"/>
       <c r="L77" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>4017532.82</v>
+        <v>27763.77</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2080-7102-CM26</t>
+          <t>1057402-7716-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5170,42 +5170,42 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Enviada a Proveedor</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Magallanes y Antártica</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.825.774-4</t>
         </is>
       </c>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>8774488.800000001</v>
+        <v>3908.56</v>
       </c>
     </row>
     <row r="79">
@@ -5262,17 +5262,17 @@
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>19350392.46</v>
+        <v>20785.19</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>1057402-7716-CM26</t>
+          <t>1057539-5748-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5287,53 +5287,53 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>3638753.44</v>
+        <v>72323.72</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>812030-765-CM26</t>
+          <t>1952-1929-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5348,7 +5348,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -5358,43 +5358,43 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.602.248-2</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>Hospital Villarrica</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>GLOBALMED SPA</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>9692550</v>
+        <v>45742.47</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1057501-7870-CM26</t>
+          <t>608-7408-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5409,53 +5409,53 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>MEDYSSEY</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.485.678-3</t>
         </is>
       </c>
       <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>51509567.69</v>
+        <v>4358.79</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1057501-7867-CM26</t>
+          <t>2111-10881-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5470,22 +5470,22 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -5495,28 +5495,28 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.901.400-4</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>53734918.86</v>
+        <v>2684.3</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1057501-7871-CM26</t>
+          <t>2107-1497-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5531,7 +5531,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -5541,43 +5541,43 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.901.400-4</t>
         </is>
       </c>
       <c r="K84" t="inlineStr"/>
       <c r="L84" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>25847240.3</v>
+        <v>9026.91</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1952-1929-CM26</t>
+          <t>1057509-8182-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5602,43 +5602,43 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.602.248-2</t>
+          <t>61.607.001-0</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hospital Villarrica</t>
+          <t>HOSPITAL CLINICO HERMINDA MARTIN</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>GLOBALMED SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
       <c r="L85" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>42584864</v>
+        <v>2400.44</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1057539-5748-CM26</t>
+          <t>3378-6339-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5653,7 +5653,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5663,43 +5663,43 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>67331216.26000001</v>
+        <v>2501.94</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>608-7408-CM26</t>
+          <t>4502-682-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5714,7 +5714,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -5724,43 +5724,43 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>MEDYSSEY</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>76.485.678-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>4057900</v>
+        <v>4115.92</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2111-10881-CM26</t>
+          <t>2258-6051-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5775,53 +5775,53 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>2499000</v>
+        <v>3354.09</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>886954-3488-CM26</t>
+          <t>3328-1738-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5841,48 +5841,48 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.602.189-3</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
+          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>BIOIMPLANTES SA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.214.144-2</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>37329705</v>
+        <v>5648.29</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>3328-1738-CM26</t>
+          <t>886954-3488-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5902,48 +5902,48 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.602.189-3</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
+          <t>HOSPITAL GUILLERMO GRANT BENAVENTE DE CO</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Bío-Bío</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>BIOIMPLANTES SA</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.214.144-2</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>5258383.9</v>
+        <v>40097.65</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2258-6051-CM26</t>
+          <t>1549-3226-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -5963,48 +5963,48 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>3122560</v>
+        <v>69079.46000000001</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1549-3226-CM26</t>
+          <t>4776-382-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6019,22 +6019,22 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.108.000-k</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>CAJA DE PREVISION DE LA DEFENSA NACIONAL</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -6044,28 +6044,28 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>64310908.2</v>
+        <v>2770.58</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3378-6339-CM26</t>
+          <t>3191-3857-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6080,7 +6080,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6090,43 +6090,43 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>EJERCITO DE CHILE HOSPITAL MILITAR DE SANTIAGO</t>
+          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>2329228.65</v>
+        <v>25594.53</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1057509-8182-CM26</t>
+          <t>1549-3291-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6141,7 +6141,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6151,43 +6151,43 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.607.001-0</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO HERMINDA MARTIN</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2234736.7</v>
+        <v>3521.8</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>4502-682-CM26</t>
+          <t>812030-776-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6202,53 +6202,53 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>3831800</v>
+        <v>45617.07</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2107-1497-CM26</t>
+          <t>898-2497-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6263,7 +6263,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -6273,43 +6273,43 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.602.148-6</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
+          <t>HOSPITAL CLAUDIO VICUNA</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>ARENYS MED S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>76.901.400-4</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>8403780</v>
+        <v>2585.87</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>3191-3857-CM26</t>
+          <t>2258-5597-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6324,53 +6324,53 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>HOSPITAL NAVAL ALMIRANTE NEF</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>23827736.52</v>
+        <v>20550.59</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>4776-382-CM26</t>
+          <t>2258-5681-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -6395,43 +6395,43 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.108.000-k</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>CAJA DE PREVISION DE LA DEFENSA NACIONAL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>2579325</v>
+        <v>10211.24</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1549-3291-CM26</t>
+          <t>5083-376-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -6456,43 +6456,43 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
+          <t>MEDYSSEY</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>76.485.678-3</t>
         </is>
       </c>
       <c r="K99" t="inlineStr"/>
       <c r="L99" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>3278688</v>
+        <v>3201.42</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>812030-776-CM26</t>
+          <t>1704-4096-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6507,27 +6507,27 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6543,17 +6543,17 @@
       <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>42468125</v>
+        <v>16151.69</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2258-5597-CM26</t>
+          <t>1057501-8311-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6568,53 +6568,53 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
       <c r="L101" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>19131981.05</v>
+        <v>6022.45</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2258-5681-CM26</t>
+          <t>2080-7285-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6629,53 +6629,53 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Lib. Gral. Bdo. O'Higgins</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>Productos Medicos Limitada</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.073.910-k</t>
         </is>
       </c>
       <c r="K102" t="inlineStr"/>
       <c r="L102" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>9506360.220000001</v>
+        <v>25140.58</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>5083-376-CM26</t>
+          <t>1549-3347-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6690,7 +6690,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -6700,43 +6700,43 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>MEDYSSEY</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>76.485.678-3</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
       <c r="L103" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>2980426.4</v>
+        <v>49391.07</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>898-2497-CM26</t>
+          <t>2069-6748-CM26</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -6761,43 +6761,43 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>2407370</v>
+        <v>3477.5</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>1704-4096-CM26</t>
+          <t>2069-6712-CM26</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -6812,7 +6812,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6822,17 +6822,17 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6848,17 +6848,17 @@
       <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>15036742.42</v>
+        <v>5299.59</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2069-6712-CM26</t>
+          <t>2069-6759-CM26</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -6909,17 +6909,17 @@
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>4933761.42</v>
+        <v>3298.79</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2069-6748-CM26</t>
+          <t>3328-1937-CM26</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -6959,388 +6959,22 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>HOSPITALIA Productos Medicos Ltda</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>3237444.98</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>2069-6759-CM26</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>2239-15-LR25</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>61.608.101-2</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
-        </is>
-      </c>
-      <c r="J108" t="inlineStr">
-        <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K108" t="inlineStr"/>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M108" s="2" t="n">
-        <v>3071071.08</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>2080-7285-CM26</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>2239-15-LR25</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>61.602.138-9</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>Productos Medicos Limitada</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>78.073.910-k</t>
-        </is>
-      </c>
-      <c r="K109" t="inlineStr"/>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M109" s="2" t="n">
-        <v>23405122.3</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>1057501-8311-CM26</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>2239-15-LR25</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>61.608.502-6</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
-        </is>
-      </c>
-      <c r="J110" t="inlineStr">
-        <is>
-          <t>78.566.250-4</t>
-        </is>
-      </c>
-      <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M110" s="2" t="n">
-        <v>5606723.08</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>1549-3347-CM26</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>2239-15-LR25</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>61.608.002-4</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
-        </is>
-      </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M111" s="2" t="n">
-        <v>45981600</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>3328-1937-CM26</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>2239-15-LR25</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>61.103.007-K</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>HOSPITAL CLINICO DE LA FUERZA AEREA GRAL DR RAUL YAZIGI JAUREGUI</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>HOSPITALIA Productos Medicos Ltda</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M112" s="2" t="n">
-        <v>18735360</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>5083-398-CM26</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>2239-15-LR25</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>jul-2026</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>Enviada a Proveedor</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>61.606.903-9</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Maule</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>CLP</t>
-        </is>
-      </c>
-      <c r="M113" s="2" t="n">
-        <v>3097279.64</v>
+        <v>20124.56</v>
       </c>
     </row>
   </sheetData>
